--- a/backend/public/templates/template_siswa.xlsx
+++ b/backend/public/templates/template_siswa.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,41 +418,58 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Hendra Wijaya</v>
+        <v>Rivia Siswa</v>
       </c>
       <c r="B2" t="str">
-        <v>hendra@example.com</v>
+        <v>riviasr1212@gmail.com</v>
       </c>
       <c r="C2" t="str">
-        <v>12345</v>
+        <v>2024001</v>
       </c>
       <c r="D2" t="str">
         <v>0012345678</v>
       </c>
       <c r="E2" t="str">
-        <v>X RPL 1</v>
+        <v>10 RPL A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Budi Santoso</v>
+        <v>Hendra Wijaya</v>
       </c>
       <c r="B3" t="str">
-        <v>budi@example.com</v>
+        <v>hendra@siswa.sekolah.sch.id</v>
       </c>
       <c r="C3" t="str">
-        <v>12346</v>
+        <v>2024002</v>
       </c>
       <c r="D3" t="str">
         <v>0012345679</v>
       </c>
       <c r="E3" t="str">
-        <v>X RPL 1</v>
+        <v>10 RPL A</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Budi Santoso</v>
+      </c>
+      <c r="B4" t="str">
+        <v>budi@siswa.sekolah.sch.id</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2024003</v>
+      </c>
+      <c r="D4" t="str">
+        <v>0012345680</v>
+      </c>
+      <c r="E4" t="str">
+        <v>10 TKJ A</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
   </ignoredErrors>
 </worksheet>
 </file>